--- a/datafiles/Employee_Template.xlsx
+++ b/datafiles/Employee_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gamer\Documents\Egyetem\MSC\3. félév\Dipterv1\PerfEval\datafiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E582A7F0-43B0-4118-9AA7-33BD27298683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3FD52D-EF55-4003-8C6E-A1C5819CFCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,12 +43,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -72,8 +81,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -364,16 +374,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
